--- a/data/availability/projects/palm-hills-developments/palm-hills-one.xlsx
+++ b/data/availability/projects/palm-hills-developments/palm-hills-one.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,7 +809,6 @@
       <c r="G2" t="n">
         <v>358</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -820,7 +819,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -842,7 +841,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -866,7 +865,6 @@
       <c r="G3" t="n">
         <v>403</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -877,7 +875,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -899,7 +897,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -923,7 +921,6 @@
       <c r="G4" t="n">
         <v>673</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -934,7 +931,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -956,7 +953,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -980,7 +977,6 @@
       <c r="G5" t="n">
         <v>673</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -991,7 +987,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1037,7 +1033,6 @@
       <c r="G6" t="n">
         <v>340</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1048,7 +1043,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1094,7 +1089,6 @@
       <c r="G7" t="n">
         <v>340</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1105,7 +1099,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1151,7 +1145,6 @@
       <c r="G8" t="n">
         <v>340</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1162,7 +1155,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1208,7 +1201,6 @@
       <c r="G9" t="n">
         <v>340</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1219,7 +1211,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1265,7 +1257,6 @@
       <c r="G10" t="n">
         <v>340</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1276,7 +1267,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1322,7 +1313,6 @@
       <c r="G11" t="n">
         <v>340</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1333,7 +1323,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1355,7 +1345,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1379,7 +1369,6 @@
       <c r="G12" t="n">
         <v>358</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1390,7 +1379,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1412,7 +1401,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1436,7 +1425,6 @@
       <c r="G13" t="n">
         <v>358</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1447,7 +1435,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1469,7 +1457,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1493,7 +1481,6 @@
       <c r="G14" t="n">
         <v>358</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1504,7 +1491,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1526,7 +1513,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1550,7 +1537,6 @@
       <c r="G15" t="n">
         <v>358</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1561,7 +1547,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1583,7 +1569,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1607,7 +1593,6 @@
       <c r="G16" t="n">
         <v>518</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1618,7 +1603,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1640,7 +1625,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1664,7 +1649,6 @@
       <c r="G17" t="n">
         <v>518</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1675,7 +1659,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1697,7 +1681,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1721,7 +1705,6 @@
       <c r="G18" t="n">
         <v>385</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1732,7 +1715,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1754,7 +1737,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1778,7 +1761,6 @@
       <c r="G19" t="n">
         <v>385</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1789,7 +1771,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1811,7 +1793,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1835,7 +1817,6 @@
       <c r="G20" t="n">
         <v>518</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1846,7 +1827,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1868,7 +1849,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1892,7 +1873,6 @@
       <c r="G21" t="n">
         <v>518</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1903,7 +1883,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1925,7 +1905,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1949,7 +1929,6 @@
       <c r="G22" t="n">
         <v>518</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1960,7 +1939,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1982,7 +1961,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2006,7 +1985,6 @@
       <c r="G23" t="n">
         <v>385</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2017,7 +1995,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2039,7 +2017,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2063,7 +2041,6 @@
       <c r="G24" t="n">
         <v>385</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2074,7 +2051,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2096,7 +2073,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2120,7 +2097,6 @@
       <c r="G25" t="n">
         <v>358</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2131,7 +2107,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2153,7 +2129,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2177,7 +2153,6 @@
       <c r="G26" t="n">
         <v>358</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2188,7 +2163,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2210,7 +2185,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2234,7 +2209,6 @@
       <c r="G27" t="n">
         <v>358</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2245,7 +2219,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2267,7 +2241,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2291,7 +2265,6 @@
       <c r="G28" t="n">
         <v>358</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2302,7 +2275,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2348,7 +2321,6 @@
       <c r="G29" t="n">
         <v>340</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2359,7 +2331,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2405,7 +2377,6 @@
       <c r="G30" t="n">
         <v>340</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2416,7 +2387,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2438,7 +2409,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2462,7 +2433,6 @@
       <c r="G31" t="n">
         <v>358</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2473,7 +2443,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2495,7 +2465,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2519,7 +2489,6 @@
       <c r="G32" t="n">
         <v>358</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2530,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2552,7 +2521,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2576,7 +2545,6 @@
       <c r="G33" t="n">
         <v>358</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2587,7 +2555,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2609,7 +2577,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2633,7 +2601,6 @@
       <c r="G34" t="n">
         <v>358</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2644,7 +2611,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2666,7 +2633,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2690,7 +2657,6 @@
       <c r="G35" t="n">
         <v>358</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2701,7 +2667,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2723,7 +2689,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2747,7 +2713,6 @@
       <c r="G36" t="n">
         <v>358</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2758,7 +2723,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2780,7 +2745,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2804,7 +2769,6 @@
       <c r="G37" t="n">
         <v>358</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2815,7 +2779,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2837,7 +2801,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2861,7 +2825,6 @@
       <c r="G38" t="n">
         <v>358</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2872,7 +2835,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2894,7 +2857,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2918,7 +2881,6 @@
       <c r="G39" t="n">
         <v>358</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2929,7 +2891,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2951,7 +2913,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2975,7 +2937,6 @@
       <c r="G40" t="n">
         <v>195</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2986,7 +2947,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3008,7 +2969,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3032,7 +2993,6 @@
       <c r="G41" t="n">
         <v>195</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3043,7 +3003,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3065,7 +3025,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3089,7 +3049,6 @@
       <c r="G42" t="n">
         <v>195</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3100,7 +3059,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3122,7 +3081,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3146,7 +3105,6 @@
       <c r="G43" t="n">
         <v>195</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3157,7 +3115,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3179,7 +3137,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3203,7 +3161,6 @@
       <c r="G44" t="n">
         <v>195</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3214,7 +3171,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3236,7 +3193,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3260,7 +3217,6 @@
       <c r="G45" t="n">
         <v>195</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3271,7 +3227,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3293,7 +3249,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3317,7 +3273,6 @@
       <c r="G46" t="n">
         <v>308</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3328,7 +3283,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3350,7 +3305,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3374,7 +3329,6 @@
       <c r="G47" t="n">
         <v>308</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3385,7 +3339,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3407,7 +3361,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3431,7 +3385,6 @@
       <c r="G48" t="n">
         <v>195</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3442,7 +3395,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3464,7 +3417,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3488,7 +3441,6 @@
       <c r="G49" t="n">
         <v>195</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3499,7 +3451,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3521,7 +3473,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3545,7 +3497,6 @@
       <c r="G50" t="n">
         <v>403</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3556,7 +3507,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3602,7 +3553,6 @@
       <c r="G51" t="n">
         <v>358</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3613,7 +3563,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3659,7 +3609,6 @@
       <c r="G52" t="n">
         <v>358</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3670,7 +3619,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3716,7 +3665,6 @@
       <c r="G53" t="n">
         <v>358</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3727,7 +3675,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3773,7 +3721,6 @@
       <c r="G54" t="n">
         <v>358</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3784,7 +3731,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
